--- a/docs/LLM-연동-API-명세서.xlsx
+++ b/docs/LLM-연동-API-명세서.xlsx
@@ -8409,7 +8409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8651,7 +8651,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="44.5" customHeight="1">
+    <row r="10" ht="71.5" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>7</t>
@@ -8659,123 +8659,125 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>IF-LLM-003</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>[계산 필요] 컬럼을 지표에 없는 방식으로 계산 (지표가 그 컬럼에 쓰지 않은 집계, 지표 없는 컬럼의 SUM, AVG, 집계끼리의 산술. MIN, MAX 하나는 허용)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>고른 지표가 그 컬럼을 쓰면: 고칠 점('… 지표의 계산 식을 그대로 쓰십시오')을 붙여 다시 요청
+고른 지표에 그 컬럼이 없으면: 다시 묻지 않음</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>앞의 경우 3번 실패하면 종료, 뒤의 경우 바로 종료</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>앞의 경우 error: 마지막 오류 문장
+뒤의 경우 '지표 등록이 필요합니다 — {테이블}.{컬럼}({설명}) 은 계산이 필요한 컬럼인데 이 계산의 지표가 없습니다' 와 지표 등록 버튼</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44.5" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>IF-LLM-004</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>답변에 JSON 이 없음. sql 과 unsure 가 둘 다 빔</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>'형식이 틀렸습니다: …' 또는 'sql 이 비었습니다. SQL 을 적거나, 정할 수 없으면 unsure 에 이유를 적으십시오.' 를 붙여 다시 요청</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>3번까지</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>마지막 초안 (sql 이 비어 있을 수 있음)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>IF-LLM-004</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>unsure 만 있음 (계산 방식을 정하지 못함)</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>더 묻지 않음</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>바로 종료</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>초안 화면에 정하지 못한 이유</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="44.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+    <row r="13" ht="44.5" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>IF-LLM-004</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>등록 확인 실패: AST 변환, 컴파일, 실행 전 확인(순번 참조, 큰 테이블 전체 스캔), 결과 비교</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>대상 DB 에서 실행하지 않음(실행 전 확인). 고칠 점('{단계}: {오류}' 다음 줄에 '고쳐서 JSON 으로 다시 답하십시오.')을 붙여 다시 요청</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>3번 실패하면 종료</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>초안과 마지막 확인 결과(단계, 오류). 사람이 고쳐서 다시 확인한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="31" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>IF-LLM-004</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>값 샘플을 읽지 못함 (대상 DB 접속 실패, 쓸 인덱스 없음, 조회 10초 초과)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>샘플 없이 초안을 쓴다</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>(정상 진행)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>sample.note 에 이유</t>
         </is>
       </c>
     </row>
@@ -8787,27 +8789,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>IF-LLM 공통</t>
+          <t>IF-LLM-004</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>LLM 서버 연결 실패, 응답 지연</t>
+          <t>값 샘플을 읽지 못함 (대상 DB 접속 실패, 쓸 인덱스 없음, 조회 10초 초과)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>따로 처리하지 않음. 타임아웃과 재연결은 LangChain 기본값</t>
+          <t>샘플 없이 초안을 쓴다</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>예외가 그대로 올라감</t>
+          <t>(정상 진행)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>HTTP 500. ask_log 에 기록되지 않음 (개선 필요)</t>
+          <t>sample.note 에 이유</t>
         </is>
       </c>
     </row>
@@ -8819,27 +8821,27 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>IF-SS 공통</t>
+          <t>IF-LLM 공통</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>backend/.env 에 SUPERSET_URL, SUPERSET_USERNAME, SUPERSET_PASSWORD 가 없음</t>
+          <t>LLM 서버 연결 실패, 응답 지연</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Superset 을 부르지 않음</t>
+          <t>따로 처리하지 않음. 타임아웃과 재연결은 LangChain 기본값</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>바로 종료</t>
+          <t>예외가 그대로 올라감</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>HTTP 400 'Superset 연동 설정이 없습니다 …'</t>
+          <t>HTTP 500. ask_log 에 기록되지 않음 (개선 필요)</t>
         </is>
       </c>
     </row>
@@ -8856,116 +8858,148 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
+          <t>backend/.env 에 SUPERSET_URL, SUPERSET_USERNAME, SUPERSET_PASSWORD 가 없음</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Superset 을 부르지 않음</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>바로 종료</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>HTTP 400 'Superset 연동 설정이 없습니다 …'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="31" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>IF-SS 공통</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t>Superset 에 접속하지 못함 (꺼짐, 인증서 검증 실패, 30초 초과)</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>다시 시도하지 않음</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>바로 종료</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>HTTP 502 'Superset({URL}) 에 접속하지 못했습니다: {이유}'</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="44.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>IF-SS 공통</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Superset 이 400 이상으로 거절 (로그인 실패, CSRF, 대상 DB 접속 실패, SQL 오류 등)</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>응답의 errors[0].message 또는 message 를 읽음</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>바로 종료</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>HTTP 502 'Superset 이 요청을 거절했습니다 ({방식} {경로}, {상태}): {이유}'</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="31" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>IF-SS-002</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Oracle 시스템</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Superset 을 부르지 않음 (이미지에 드라이버 없음)</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>바로 종료</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>HTTP 400 'Superset 에 oracle 드라이버가 없어 연결할 수 없습니다'</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="44.5" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="44.5" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>IF-SS-003, 004</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Superset 에 연결하지 않은 시스템. SQL 이 없는 질문 기록</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Superset 을 부르지 않음</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>바로 종료</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>HTTP 400 '… 은 아직 Superset 에 연결하지 않았습니다' / 'SQL 을 만들지 못한 질문입니다'</t>
         </is>
@@ -9613,7 +9647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9781,6 +9815,23 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>IF-LLM-003</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>[계산 필요] 컬럼의 계산은 고른 지표가 그 컬럼에 쓴 집계 함수로만 컴파일 (compiler.CalcColumnError). 지표가 없으면 '지표 등록이 필요합니다' 로 끝냄</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
